--- a/data/history/2025-06/运营报告_20250601_000000.xlsx
+++ b/data/history/2025-06/运营报告_20250601_000000.xlsx
@@ -18,7 +18,8 @@
     <sheet name="负责人待办" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="通知复盘" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="闭环复盘" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="反馈异常" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="问题生命周期" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="反馈待确认" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -620,7 +621,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260607_071244</t>
+          <t>20260607_072428</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -661,7 +662,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-07 07:12:44</t>
+          <t>2026-06-07 07:24:28</t>
         </is>
       </c>
     </row>
@@ -676,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,20 +703,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>复发问题数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>超期未处理数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>复发问题数</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>即将超期数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均处理天数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最长未处理天数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>问题总数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>本月闭环率(%)</t>
         </is>
@@ -724,7 +740,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -734,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -747,6 +763,52 @@
       </c>
       <c r="H2" t="n">
         <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -760,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,91 +833,2875 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>处理状态</t>
+          <t>事件类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>处理人</t>
+          <t>事件时间</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>处理时间</t>
+          <t>事件描述</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>错误原因</t>
+          <t>关联批次</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>车场名称</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NONEXIST001</t>
+          <t>027774C8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>驳回</t>
+          <t>首次发现</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>运营人员2</t>
+          <t>2026-06-07 07:22:23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-05 10:00:00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>这是第5条处理反馈，状态为驳回</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>问题ID不存在或不匹配</t>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 31.5%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>收入突降</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NONEXIST002</t>
+          <t>027774C8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>驳回</t>
+          <t>重复出现</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>运营人员3</t>
+          <t>2026-06-07 07:22:53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-06 10:00:00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>这是第6条处理反馈，状态为驳回</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>问题ID不存在或不匹配</t>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>027774C8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>027774C8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>发送通知</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>发送负责人待办通知</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20260607_072349</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 33.0%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 33.2%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 73.7%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>发送通知</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>发送负责人待办通知</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>20260607_072349</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 33.0%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>发送通知</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>发送负责人待办通知</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20260607_072349</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 32.9%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>发送通知</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>发送负责人待办通知</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>20260607_072349</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 32.2%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>状态变更: 待处理 → 驳回，备注: 数据不全无法处理</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>运营3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>状态变更: 驳回 → 驳回，备注: 数据不全无法处理</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>运营3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2025-06-11 14:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>状态变更: 驳回 → 已处理，备注: 已补充入出场数据字段</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>运营B</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 34.8%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025-06-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>状态变更: 待处理 → 已处理，备注: 已补全缺失日期数据</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-06-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>状态变更: 已处理 → 已处理，备注: 已补全缺失日期数据</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>首次发现: 缺失日期 - 缺失 3 天数据</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺失日期</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺失日期</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺失日期</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>发送通知</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>发送负责人待办通知</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>20260607_072349</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 32.3%</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>发送通知</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>发送负责人待办通知</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>20260607_072349</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>车场名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>异常描述</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>处理状态</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>候选问题数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>候选问题ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>商业街直营</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>运营A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-06-10 10:00:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>上月收入突降问题已彻底解决</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>64825C28;568751B9</t>
         </is>
       </c>
     </row>
